--- a/Model objective analysis/data/Starting_point.xlsx
+++ b/Model objective analysis/data/Starting_point.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Model objective analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{E4667220-B6D3-44CA-BB2C-7EE709A98D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{763E31CA-4781-4676-997C-16FD1A5B006D}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{E4667220-B6D3-44CA-BB2C-7EE709A98D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A50D6B5B-10B4-47A2-BE44-838E5563AE3C}"/>
   <bookViews>
-    <workbookView xWindow="13550" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_start" sheetId="2" r:id="rId1"/>
@@ -290,6 +290,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1190,7 +1194,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">

--- a/Model objective analysis/data/Starting_point.xlsx
+++ b/Model objective analysis/data/Starting_point.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Model objective analysis/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{E4667220-B6D3-44CA-BB2C-7EE709A98D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A50D6B5B-10B4-47A2-BE44-838E5563AE3C}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{E4667220-B6D3-44CA-BB2C-7EE709A98D96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D300E7E3-C696-4B80-8BDB-FCFD9DB772FA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13550" yWindow="-7070" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="F_start" sheetId="2" r:id="rId1"/>
@@ -1194,7 +1194,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1353,7 +1353,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
